--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20222.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="31">
   <si>
     <t>Mat</t>
   </si>
@@ -76,13 +76,40 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
     <t>CASTAÑEDA</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>LEONEL FELIPE</t>
+  </si>
+  <si>
+    <t>ERIK</t>
+  </si>
+  <si>
     <t>PAUL ARAVIER</t>
+  </si>
+  <si>
+    <t>JOSE RAUL</t>
   </si>
 </sst>
 </file>
@@ -782,7 +809,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -814,16 +841,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920072</v>
+        <v>22330051920184</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -832,6 +859,75 @@
         <v>11</v>
       </c>
       <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>22330051920202</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920072</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>22330051920036</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20222.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="42">
   <si>
     <t>Mat</t>
   </si>
@@ -82,34 +82,67 @@
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
     <t>GIL</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>ROSAS</t>
   </si>
   <si>
     <t>COLOHUA</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
     <t>CASTAÑEDA</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>LEONEL FELIPE</t>
   </si>
   <si>
     <t>ERIK</t>
   </si>
   <si>
+    <t>KEVIN ISAAC</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>NEMESIO NAHIM</t>
+  </si>
+  <si>
     <t>PAUL ARAVIER</t>
   </si>
   <si>
     <t>JOSE RAUL</t>
+  </si>
+  <si>
+    <t>ARIEL</t>
   </si>
 </sst>
 </file>
@@ -809,7 +842,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -847,10 +880,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -870,10 +903,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -887,47 +920,139 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920072</v>
+        <v>21330051920005</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920036</v>
+        <v>20330051920089</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920023</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920072</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920036</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920012</v>
+      </c>
+      <c r="B9" t="s">
         <v>26</v>
       </c>
-      <c r="D5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5">
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20222.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="44">
   <si>
     <t>Mat</t>
   </si>
@@ -76,67 +76,73 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
     <t>GIL</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
     <t>ROSAS</t>
   </si>
   <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
+    <t>ABDIEL NOE</t>
+  </si>
+  <si>
+    <t>ERIK</t>
+  </si>
+  <si>
+    <t>KEVIN ISAAC</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>NEMESIO NAHIM</t>
+  </si>
+  <si>
+    <t>PAUL ARAVIER</t>
+  </si>
+  <si>
     <t>LEONEL FELIPE</t>
-  </si>
-  <si>
-    <t>ERIK</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>NEMESIO NAHIM</t>
-  </si>
-  <si>
-    <t>PAUL ARAVIER</t>
   </si>
   <si>
     <t>JOSE RAUL</t>
@@ -842,7 +848,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -874,7 +880,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920184</v>
+        <v>22330051920180</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
@@ -883,7 +889,7 @@
         <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -906,7 +912,7 @@
         <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -929,7 +935,7 @@
         <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -952,7 +958,7 @@
         <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -972,10 +978,10 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -998,7 +1004,7 @@
         <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1012,7 +1018,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920036</v>
+        <v>22330051920184</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
@@ -1021,13 +1027,13 @@
         <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1035,7 +1041,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920012</v>
+        <v>22330051920036</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
@@ -1044,15 +1050,38 @@
         <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920012</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" t="s">
         <v>9</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F10" t="s">
         <v>12</v>
       </c>
-      <c r="G9">
+      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20222.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="41">
   <si>
     <t>Mat</t>
   </si>
@@ -76,76 +76,67 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
     <t>MIXCOHA</t>
   </si>
   <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
     <t>SARMIENTO</t>
   </si>
   <si>
     <t>CARRERA</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>BAROJAS</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
     <t>CASTAÑEDA</t>
   </si>
   <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
+    <t>DIEGO IVAN</t>
+  </si>
+  <si>
     <t>ABDIEL NOE</t>
   </si>
   <si>
     <t>ERIK</t>
   </si>
   <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
     <t>ALEJANDRO</t>
   </si>
   <si>
+    <t>ELI ANTONIO</t>
+  </si>
+  <si>
     <t>NEMESIO NAHIM</t>
   </si>
   <si>
     <t>PAUL ARAVIER</t>
-  </si>
-  <si>
-    <t>LEONEL FELIPE</t>
-  </si>
-  <si>
-    <t>JOSE RAUL</t>
   </si>
   <si>
     <t>ARIEL</t>
@@ -666,16 +657,19 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>89.19</v>
+      </c>
+      <c r="H2">
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -689,16 +683,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>42.42</v>
+      </c>
+      <c r="H3">
+        <v>6.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -777,16 +774,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>86.48999999999999</v>
+        <v>89.19</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -803,13 +800,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>45.45</v>
+        <v>42.42</v>
       </c>
       <c r="H3">
         <v>6.1</v>
@@ -848,7 +845,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -880,7 +877,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920180</v>
+        <v>20330051920090</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
@@ -889,7 +886,7 @@
         <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -903,16 +900,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920202</v>
+        <v>22330051920180</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -926,22 +923,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920005</v>
+        <v>22330051920202</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -955,10 +952,10 @@
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -972,16 +969,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920023</v>
+        <v>20330051920366</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -995,39 +992,39 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920072</v>
+        <v>21330051920023</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920184</v>
+        <v>20330051920072</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1041,47 +1038,24 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920036</v>
+        <v>21330051920012</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920012</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20222.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="39">
   <si>
     <t>Mat</t>
   </si>
@@ -76,12 +76,12 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
@@ -94,12 +94,12 @@
     <t>SARMIENTO</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
     <t>BAROJAS</t>
   </si>
   <si>
@@ -112,18 +112,15 @@
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
+    <t>PAUL ARAVIER</t>
+  </si>
+  <si>
     <t>DIEGO IVAN</t>
   </si>
   <si>
-    <t>ABDIEL NOE</t>
-  </si>
-  <si>
     <t>ERIK</t>
   </si>
   <si>
@@ -134,9 +131,6 @@
   </si>
   <si>
     <t>NEMESIO NAHIM</t>
-  </si>
-  <si>
-    <t>PAUL ARAVIER</t>
   </si>
   <si>
     <t>ARIEL</t>
@@ -845,7 +839,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -877,16 +871,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920090</v>
+        <v>20330051920072</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -900,16 +894,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920180</v>
+        <v>20330051920090</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -932,7 +926,7 @@
         <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -955,7 +949,7 @@
         <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -978,7 +972,7 @@
         <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1001,7 +995,7 @@
         <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1015,7 +1009,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920072</v>
+        <v>21330051920012</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
@@ -1024,38 +1018,15 @@
         <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920012</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20222.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="34">
   <si>
     <t>Mat</t>
   </si>
@@ -85,18 +85,12 @@
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>MIXCOHA</t>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>NAJERA</t>
   </si>
   <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>CASTAÑEDA</t>
   </si>
   <si>
@@ -106,15 +100,12 @@
     <t>COLOHUA</t>
   </si>
   <si>
-    <t>EVARISTO</t>
+    <t>FLORES</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>PAUL ARAVIER</t>
   </si>
   <si>
@@ -124,16 +115,10 @@
     <t>ERIK</t>
   </si>
   <si>
-    <t>ALEJANDRO</t>
+    <t>ARIEL</t>
   </si>
   <si>
     <t>ELI ANTONIO</t>
-  </si>
-  <si>
-    <t>NEMESIO NAHIM</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
   </si>
 </sst>
 </file>
@@ -839,7 +824,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -877,10 +862,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -900,10 +885,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -923,10 +908,10 @@
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -940,16 +925,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920089</v>
+        <v>21330051920012</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -969,10 +954,10 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -982,52 +967,6 @@
       </c>
       <c r="G6">
         <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920023</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920012</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20222.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20222.xlsx
@@ -688,16 +688,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>60.61</v>
+      </c>
+      <c r="H4">
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -805,16 +808,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>57.58</v>
+        <v>60.61</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20222.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -82,43 +82,40 @@
     <t>MORALES</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
     <t>CASTAÑEDA</t>
   </si>
   <si>
     <t>BAROJAS</t>
   </si>
   <si>
-    <t>COLOHUA</t>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>PAUL ARAVIER</t>
   </si>
   <si>
     <t>DIEGO IVAN</t>
   </si>
   <si>
-    <t>ERIK</t>
+    <t>ELI ANTONIO</t>
+  </si>
+  <si>
+    <t>NEMESIO NAHIM</t>
   </si>
   <si>
     <t>ARIEL</t>
-  </si>
-  <si>
-    <t>ELI ANTONIO</t>
   </si>
 </sst>
 </file>
@@ -782,16 +779,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>42.42</v>
+        <v>63.64</v>
       </c>
       <c r="H3">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -868,7 +865,7 @@
         <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -891,7 +888,7 @@
         <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -905,7 +902,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920202</v>
+        <v>20330051920366</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
@@ -914,13 +911,13 @@
         <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -928,16 +925,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920012</v>
+        <v>21330051920023</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -951,16 +948,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920366</v>
+        <v>21330051920012</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -969,7 +966,7 @@
         <v>12</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20222.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="41">
   <si>
     <t>Mat</t>
   </si>
@@ -82,22 +82,37 @@
     <t>MORALES</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>NAJERA</t>
   </si>
   <si>
     <t>SARMIENTO</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>CASTAÑEDA</t>
   </si>
   <si>
     <t>BAROJAS</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
   </si>
   <si>
     <t>FLORES</t>
@@ -109,13 +124,22 @@
     <t>DIEGO IVAN</t>
   </si>
   <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>KEVIN ISAAC</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
+    <t>ARIEL</t>
+  </si>
+  <si>
     <t>ELI ANTONIO</t>
   </si>
   <si>
     <t>NEMESIO NAHIM</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
   </si>
 </sst>
 </file>
@@ -753,16 +777,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>89.19</v>
+        <v>78.38</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -824,7 +848,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -862,10 +886,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -885,10 +909,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -902,16 +926,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920366</v>
+        <v>21330051920195</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -925,16 +949,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920023</v>
+        <v>21330051920005</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -943,21 +967,21 @@
         <v>12</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920012</v>
+        <v>20330051920049</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -966,6 +990,75 @@
         <v>12</v>
       </c>
       <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920012</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920366</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920023</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20222.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="31">
   <si>
     <t>Mat</t>
   </si>
@@ -82,61 +82,31 @@
     <t>MORALES</t>
   </si>
   <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
+    <t>BAROJAS</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>BAROJAS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>PAUL ARAVIER</t>
   </si>
   <si>
     <t>DIEGO IVAN</t>
   </si>
   <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
     <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
-  </si>
-  <si>
-    <t>ELI ANTONIO</t>
   </si>
   <si>
     <t>NEMESIO NAHIM</t>
@@ -829,16 +799,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>60.61</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -848,7 +818,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -886,10 +856,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
         <v>27</v>
-      </c>
-      <c r="D2" t="s">
-        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -909,10 +879,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
         <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -926,16 +896,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920195</v>
+        <v>20330051920049</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
         <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -944,21 +914,21 @@
         <v>12</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920005</v>
+        <v>21330051920023</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
         <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>36</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -967,98 +937,6 @@
         <v>12</v>
       </c>
       <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920049</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920012</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920366</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920023</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20222.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="37">
   <si>
     <t>Mat</t>
   </si>
@@ -79,9 +79,15 @@
     <t>CARRERA</t>
   </si>
   <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>CUATRA</t>
   </si>
   <si>
@@ -91,9 +97,15 @@
     <t>CASTAÑEDA</t>
   </si>
   <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
     <t>BAROJAS</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>COYOHUA</t>
   </si>
   <si>
@@ -103,7 +115,13 @@
     <t>PAUL ARAVIER</t>
   </si>
   <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
     <t>DIEGO IVAN</t>
+  </si>
+  <si>
+    <t>JULIAN DAVID</t>
   </si>
   <si>
     <t>RAFAEL</t>
@@ -818,7 +836,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -856,10 +874,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -873,16 +891,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920090</v>
+        <v>22330051920190</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -896,47 +914,93 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920049</v>
+        <v>20330051920090</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920023</v>
+        <v>22330051920045</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920049</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920023</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
         <v>30</v>
       </c>
-      <c r="E5" t="s">
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
         <v>9</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F7" t="s">
         <v>12</v>
       </c>
-      <c r="G5">
+      <c r="G7">
         <v>1</v>
       </c>
     </row>
